--- a/Config/Excel/hero.xlsx
+++ b/Config/Excel/hero.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>小黄</t>
+  </si>
+  <si>
+    <t>小蓝</t>
+  </si>
+  <si>
+    <t>小黑</t>
   </si>
 </sst>
 </file>
@@ -1001,8 +1007,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -1097,6 +1103,28 @@
         <v>10</v>
       </c>
       <c r="C6" s="1">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>810003</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>810004</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
         <v>1002</v>
       </c>
     </row>
